--- a/data/K-ETS_마스터데이터.xlsx
+++ b/data/K-ETS_마스터데이터.xlsx
@@ -3335,9 +3335,6 @@
           <t>excess</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3378,9 +3375,6 @@
           <t>excess</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3421,9 +3415,6 @@
           <t>excess</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3464,9 +3455,6 @@
           <t>excess</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3507,9 +3495,6 @@
           <t>excess</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3550,9 +3535,6 @@
           <t>excess</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3596,8 +3578,6 @@
       <c r="K8" t="n">
         <v>23</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3638,9 +3618,6 @@
           <t>excess</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3681,7 +3658,6 @@
           <t>auction</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>-1</v>
       </c>
@@ -3689,21 +3665,6 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -3715,17 +3676,6 @@
           <t>흡수 I_t = rho × max(TNAC − theta_plus, 0). TNAC=직전 banking 스톡.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3738,17 +3688,6 @@
           <t>EU 임계(TNAC 상한 833Mt=연cap의 ~55%)를 한국에 비율적용하면 잉여(14%)가 항상 미달→흡수 0.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3761,17 +3700,6 @@
           <t>따라서 한국형 임계는 절대 Mt로 설정. 이 설계선택 자체가 연구결과(EU식 비율 부적용).</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3784,17 +3712,6 @@
           <t>carve_reserve=1: 예비분 85.28Mt(모형파라미터 MSR.msr_reserve_Mt)을 4차기간(2026–2030) cap 비례로 유통공급에서 차감(사전 격리). ICAP 2025: 4차 총량 2,537.3Mt은 예비분 포함 → 차감 없이는 방출이 공급 이중계상. L0(무MSR 반사실)=0.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3807,17 +3724,6 @@
           <t>theta_cap_frac: 발동임계=연cap 대비 TNAC 비율(-1=무조건). start_year: 개시연도(공란=즉시). intake_basis='auction'은 흡수상한도 그 해 경매물량(A_gov)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4397,7 +4303,6 @@
           <t>[주]</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>A_gov = 상수레버 아님: 정부공표 유상할당경로(무상할당비율 시트에서 cap 가중 도출, engine.auction_share_t; base: 2026 ~9.9% → 2030+ 23.9%). 정책패키지 v4의 통일 기준</t>
@@ -5388,7 +5293,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.55</v>
+        <v>0.575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5402,7 +5307,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-02 v2 재구성 (three gates)</t>
+          <t>가격 웨지 역산: λ=(P_obs−P_static)/(P_hotel−P_static). P_obs=22,750원(KAU2026시세 2026-06), P_static=9,862 / P_hotel=32,275(엔진 step MACC, B0=92.14Mt). scripts/calibrate_liquidity.py가 재계산·대조(불일치 시 실패). 구 0.55는 B0=70Mt 기준.</t>
         </is>
       </c>
     </row>
@@ -5736,9 +5641,6 @@
           <t>MSR·하한 없음, base cap, λ=0.55 유지(hold), 유상=정부공표경로 A_gov — 모든 효과의 기준선</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5786,9 +5688,6 @@
           <t>draft 수량규칙(L3: 초과분 흡수·20Mt/yr 방출·무취소) + 중위 하한(M_mid, 가정) + A_gov. 2026-08 가격범위 공고 전 예상 조합</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5839,8 +5738,6 @@
       <c r="J4" t="n">
         <v>2035</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5888,23 +5785,6 @@
           <t>수량약속형 운영규칙(B8): 2035 개시 사전공표, 무조건 경매물량 50% 흡수·전량취소·방출 0, 하한 없음, A_gov. 변형 그리드는 러너 quantity_frontier</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5917,16 +5797,6 @@
           <t>K-MSR = legislated institution; packages = its OPERATING RULES. Auction unified = A_gov (economy-wide auction share from 무상할당비율 sheet: ~9.9% 2026 -&gt; 23.9% 2030+, engine.auction_share_t). Gate waterfall: P0 -&gt; +draft rule(P1) -&gt; +corridor(=A) | branch: P0 -&gt; +quantity-commitment(=B). Runner v1.0</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8220,7 +8090,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>70</v>
+        <v>92.140327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8229,12 +8099,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025년말 누적 시중잉여(banking overhang) 초기스톡 B0. 2023말 70Mt 기준(2024·2025 외삽 전 보수적 적용)</t>
+          <t>2024년 관측 이월잔고 (모형 시작 은행잔고 B0)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>park2025; 4차 기본계획 2024.12; 시장잉여추정 시트</t>
+          <t>data/ets_data.xlsx '배출권이월량' 2024 등록부 실측 (이월+상쇄이월 합계). 구 70Mt 가정(park2025·4차 기본계획)은 실측으로 대체 — tests/test_data_integrity.py가 대조.</t>
         </is>
       </c>
     </row>
